--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HUELVA COMERCIO VIRIDIS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HUELVA COMERCIO VIRIDIS.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>65.3759</v>
+        <v>66.2512</v>
       </c>
       <c r="E2" t="n">
-        <v>55.7049</v>
+        <v>54.3484</v>
       </c>
       <c r="F2" t="n">
-        <v>9.6709</v>
+        <v>11.9026</v>
       </c>
       <c r="G2" t="n">
         <v>15.5081</v>
@@ -610,13 +610,13 @@
         <v>58.9215</v>
       </c>
       <c r="S2" t="n">
-        <v>4.876300000000001</v>
+        <v>5.7515</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8583</v>
+        <v>0.5018</v>
       </c>
       <c r="U2" t="n">
-        <v>3.0183</v>
+        <v>5.2497</v>
       </c>
       <c r="V2" t="n">
         <v>24.6101</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GARCIA FERNANDEZ</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>21.0643</v>
+        <v>26.27</v>
       </c>
       <c r="E3" t="n">
-        <v>7.257400000000001</v>
+        <v>24.6264</v>
       </c>
       <c r="F3" t="n">
-        <v>13.8067</v>
+        <v>1.6435</v>
       </c>
       <c r="G3" t="n">
-        <v>7.084700000000002</v>
+        <v>-11.9613</v>
       </c>
       <c r="H3" t="n">
-        <v>5.624899999999999</v>
+        <v>-2.0292</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4598</v>
+        <v>-9.932300000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>13.989</v>
+        <v>26.2951</v>
       </c>
       <c r="K3" t="n">
-        <v>11.4248</v>
+        <v>23.9677</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5644</v>
+        <v>2.3281</v>
       </c>
       <c r="M3" t="n">
-        <v>-6.9046</v>
+        <v>-38.2566</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.7997</v>
+        <v>-25.9966</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1046</v>
+        <v>-12.2601</v>
       </c>
       <c r="P3" t="n">
-        <v>9.264099999999999</v>
+        <v>-4.6322</v>
       </c>
       <c r="Q3" t="n">
-        <v>-11.1172</v>
+        <v>-62.6269</v>
       </c>
       <c r="R3" t="n">
-        <v>20.3815</v>
+        <v>57.9948</v>
       </c>
       <c r="S3" t="n">
-        <v>7.3605</v>
+        <v>2.8975</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8155</v>
+        <v>1.172</v>
       </c>
       <c r="U3" t="n">
-        <v>4.5449</v>
+        <v>1.7253</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.6453</v>
+        <v>39.9661</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>59.7863</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.2151</v>
+        <v>-19.8205</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>A. GALLEGO GÓMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>19.9363</v>
+        <v>18.671</v>
       </c>
       <c r="E4" t="n">
-        <v>20.7266</v>
+        <v>18.671</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7904999999999998</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.9613</v>
+        <v>18.671</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.0292</v>
+        <v>9.34</v>
       </c>
       <c r="I4" t="n">
-        <v>-9.932300000000001</v>
+        <v>9.331099999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>26.2951</v>
+        <v>18.671</v>
       </c>
       <c r="K4" t="n">
-        <v>23.9677</v>
+        <v>9.34</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3281</v>
+        <v>9.331099999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-38.2566</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-25.9966</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.2601</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.6322</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-62.6269</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>57.9948</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.436</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.7281</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7082000000000002</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>39.9661</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>59.7863</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.8205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GALLEGO GÓMEZ</t>
+          <t>M. GARCIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>18.671</v>
+        <v>18.2211</v>
       </c>
       <c r="E5" t="n">
-        <v>18.671</v>
+        <v>5.615699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>12.6055</v>
       </c>
       <c r="G5" t="n">
-        <v>18.671</v>
+        <v>7.084700000000002</v>
       </c>
       <c r="H5" t="n">
-        <v>9.34</v>
+        <v>5.624899999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>9.331099999999999</v>
+        <v>1.4598</v>
       </c>
       <c r="J5" t="n">
-        <v>18.671</v>
+        <v>13.989</v>
       </c>
       <c r="K5" t="n">
-        <v>9.34</v>
+        <v>11.4248</v>
       </c>
       <c r="L5" t="n">
-        <v>9.331099999999999</v>
+        <v>2.5644</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-6.9046</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-5.7997</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.1046</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>9.264099999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-11.1172</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>20.3815</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.5174</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.1738</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.3437</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.6453</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-4.2151</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>12.4802</v>
+        <v>14.198</v>
       </c>
       <c r="E6" t="n">
-        <v>7.985000000000001</v>
+        <v>9.566099999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4956</v>
+        <v>4.632000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.4123999999999994</v>
@@ -922,13 +922,13 @@
         <v>47.248</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2771</v>
+        <v>3.9948</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0837</v>
+        <v>0.4974</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3608</v>
+        <v>3.4973</v>
       </c>
       <c r="V6" t="n">
         <v>15.1646</v>
@@ -955,13 +955,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>5.6539</v>
+        <v>1.6039</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8374</v>
+        <v>-1.4054</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8166</v>
+        <v>3.008999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-4.3054</v>
@@ -1000,13 +1000,13 @@
         <v>14.267</v>
       </c>
       <c r="S7" t="n">
-        <v>8.669</v>
+        <v>4.6189</v>
       </c>
       <c r="T7" t="n">
-        <v>6.1757</v>
+        <v>1.9328</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4933</v>
+        <v>2.6861</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3773000000000002</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1273</v>
+        <v>1.1519</v>
       </c>
       <c r="E8" t="n">
         <v>1.2391</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1119</v>
+        <v>-0.0872</v>
       </c>
       <c r="G8" t="n">
         <v>0.8497</v>
@@ -1078,13 +1078,13 @@
         <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.093</v>
+        <v>-0.0684</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0623</v>
+        <v>0.4554999999999985</v>
       </c>
       <c r="E9" t="n">
-        <v>8.840800000000002</v>
+        <v>7.2998</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.778499999999999</v>
+        <v>-6.8448</v>
       </c>
       <c r="G9" t="n">
         <v>-1.500099999999999</v>
@@ -1156,13 +1156,13 @@
         <v>48.9154</v>
       </c>
       <c r="S9" t="n">
-        <v>1.883699999999999</v>
+        <v>1.277</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4308</v>
+        <v>-0.1104</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4533000000000003</v>
+        <v>1.3872</v>
       </c>
       <c r="V9" t="n">
         <v>13.4633</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="G10" t="n">
         <v>0.1306</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1034</v>
+        <v>0.1171</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9979</v>
+        <v>-0.8021</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8946</v>
+        <v>0.9192</v>
       </c>
       <c r="G11" t="n">
         <v>0.2172</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3206</v>
+        <v>-0.1001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1017</v>
+        <v>-0.0771</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1761</v>
+        <v>-0.0044</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0882</v>
+        <v>-0.0143</v>
       </c>
       <c r="G12" t="n">
         <v>0.1985</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0602</v>
+        <v>0.1116</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3144</v>
@@ -1423,10 +1423,10 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2418</v>
+        <v>-0.1438</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0124</v>
+        <v>0.0856</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2294</v>
@@ -1468,10 +1468,10 @@
         <v>0.1853</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ SANCHEZ</t>
+          <t>A. ALEMAN ROMERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.4364000000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6102</v>
+        <v>-5.4049</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.08069999999999999</v>
+        <v>4.9685</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7997</v>
+        <v>-4.3812</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0608</v>
+        <v>-7.4729</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2611</v>
+        <v>3.0919</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6314</v>
+        <v>3.441300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6314</v>
+        <v>-1.0319</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.4732</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1683</v>
+        <v>-7.8226</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4294</v>
+        <v>-6.4411</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2611</v>
+        <v>-1.3814</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1853</v>
+        <v>-5.188000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-18.7139</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1853</v>
+        <v>13.526</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0766</v>
+        <v>3.7201</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0211</v>
+        <v>1.687</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0977</v>
+        <v>2.033</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.412800000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>8.180900000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.7681</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ZAYAS CARRASCOSA</t>
+          <t>D. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0792</v>
+        <v>-0.6417</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5673</v>
+        <v>-0.6102</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5119</v>
+        <v>-0.0315</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.302</v>
+        <v>-0.7997</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.365</v>
+        <v>-1.0608</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9370000000000001</v>
+        <v>0.2611</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5884</v>
+        <v>-0.6314</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0644</v>
+        <v>-0.6314</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7136</v>
+        <v>-0.1683</v>
       </c>
       <c r="N15" t="n">
         <v>-0.4294</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2841</v>
+        <v>0.2611</v>
       </c>
       <c r="P15" t="n">
         <v>0.1853</v>
@@ -1624,13 +1624,13 @@
         <v>0.1853</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0376</v>
+        <v>-0.0274</v>
       </c>
       <c r="T15" t="n">
         <v>0.0211</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0164</v>
+        <v>-0.0485</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SANTOS IZQUIERDO</t>
+          <t>J. ZAYAS CARRASCOSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1771</v>
+        <v>-0.9566</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0332</v>
+        <v>-0.4694</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1439</v>
+        <v>-0.4872</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-1.302</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0215</v>
+        <v>-0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8294</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0215</v>
+        <v>-0.5884</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0215</v>
+        <v>0.0644</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6529</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8294</v>
+        <v>-0.7136</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.4294</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8294</v>
+        <v>-0.2841</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0547</v>
+        <v>0.1601</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0547</v>
+        <v>0.1191</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. LOPEZ BURRERO</t>
+          <t>J. SANTOS IZQUIERDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2234</v>
+        <v>-0.9812</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6855</v>
+        <v>0.1626</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5379</v>
+        <v>-1.1439</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1062</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5548</v>
+        <v>0.0215</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5514</v>
+        <v>-0.8294</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4855</v>
+        <v>0.0215</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0429</v>
+        <v>0.0215</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5284</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6207</v>
+        <v>-0.8294</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5977</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.023</v>
+        <v>-0.8294</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5613</v>
+        <v>0.1411</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2736</v>
+        <v>0.1411</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2878</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HERNANDEZ RAMOS</t>
+          <t>D. LOPEZ BURRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,61 +1810,61 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4114</v>
+        <v>-2.1495</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7552</v>
+        <v>-1.6855</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6562</v>
+        <v>-0.464</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3318</v>
+        <v>-1.1062</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1735</v>
+        <v>-0.5548</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5053</v>
+        <v>-0.5514</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6099</v>
+        <v>-0.4855</v>
       </c>
       <c r="K18" t="n">
         <v>0.0429</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6529</v>
+        <v>-0.5284</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7219</v>
+        <v>-0.6207</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1306</v>
+        <v>-0.5977</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8524</v>
+        <v>-0.023</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1532</v>
+        <v>-0.4875</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2189</v>
+        <v>-0.2736</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06569999999999999</v>
+        <v>-0.2139</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. LIMON NUNEZ</t>
+          <t>A. HERNANDEZ RAMOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0148</v>
+        <v>-2.3129</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7443</v>
+        <v>-1.7552</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2705</v>
+        <v>-0.5577</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6217999999999999</v>
+        <v>-1.3318</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0556</v>
+        <v>0.1735</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6774</v>
+        <v>-1.5053</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6972</v>
+        <v>-0.6099</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5884</v>
+        <v>0.0429</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2856</v>
+        <v>-0.6529</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07540000000000002</v>
+        <v>-0.7219</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4671</v>
+        <v>0.1306</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3918</v>
+        <v>-0.8524</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3221</v>
+        <v>-0.0547</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2736</v>
+        <v>-0.2189</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0485</v>
+        <v>0.1641</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2028</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALEMAN ROMERA</t>
+          <t>H. LIMON NUNEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.678500000000001</v>
+        <v>-2.6958</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.1152</v>
+        <v>-1.5484</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4368</v>
+        <v>-1.1474</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3812</v>
+        <v>0.6217999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.4729</v>
+        <v>-1.0556</v>
       </c>
       <c r="I20" t="n">
-        <v>3.0919</v>
+        <v>1.6774</v>
       </c>
       <c r="J20" t="n">
-        <v>3.441300000000001</v>
+        <v>0.6972</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0319</v>
+        <v>-0.5884</v>
       </c>
       <c r="L20" t="n">
-        <v>4.4732</v>
+        <v>1.2856</v>
       </c>
       <c r="M20" t="n">
-        <v>-7.8226</v>
+        <v>-0.07540000000000002</v>
       </c>
       <c r="N20" t="n">
-        <v>-6.4411</v>
+        <v>-0.4671</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3814</v>
+        <v>0.3918</v>
       </c>
       <c r="P20" t="n">
-        <v>-5.188000000000001</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q20" t="n">
-        <v>-18.7139</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>13.526</v>
+        <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5221</v>
+        <v>-0.0031</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0232</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5012999999999999</v>
+        <v>0.0746</v>
       </c>
       <c r="V20" t="n">
-        <v>5.412800000000001</v>
+        <v>-2.2028</v>
       </c>
       <c r="W20" t="n">
-        <v>8.180900000000001</v>
+        <v>-0.315</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7681</v>
+        <v>-1.8878</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8029</v>
+        <v>-11.2298</v>
       </c>
       <c r="E21" t="n">
-        <v>-10.6055</v>
+        <v>-15.2606</v>
       </c>
       <c r="F21" t="n">
-        <v>4.8026</v>
+        <v>4.0306</v>
       </c>
       <c r="G21" t="n">
         <v>5.683299999999999</v>
@@ -2092,13 +2092,13 @@
         <v>51.5098</v>
       </c>
       <c r="S21" t="n">
-        <v>8.8307</v>
+        <v>3.4032</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6395</v>
+        <v>-2.0154</v>
       </c>
       <c r="U21" t="n">
-        <v>6.1912</v>
+        <v>5.419</v>
       </c>
       <c r="V21" t="n">
         <v>-16.426</v>
@@ -2125,13 +2125,13 @@
         <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>-19.5997</v>
+        <v>-23.2655</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2974</v>
+        <v>-8.451400000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.3022</v>
+        <v>-14.814</v>
       </c>
       <c r="G22" t="n">
         <v>-14.1173</v>
@@ -2170,13 +2170,13 @@
         <v>15.3788</v>
       </c>
       <c r="S22" t="n">
-        <v>4.970000000000001</v>
+        <v>1.304</v>
       </c>
       <c r="T22" t="n">
-        <v>4.4086</v>
+        <v>1.2546</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5611999999999999</v>
+        <v>0.04959999999999987</v>
       </c>
       <c r="V22" t="n">
         <v>-7.4876</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GALLEGO GOMEZ</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,76 +2200,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-30.033</v>
+        <v>-25.7573</v>
       </c>
       <c r="E23" t="n">
-        <v>-31.2229</v>
+        <v>-5.539799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1899</v>
+        <v>-20.2174</v>
       </c>
       <c r="G23" t="n">
-        <v>-18.4335</v>
+        <v>-3.058099999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.9472</v>
+        <v>-7.0229</v>
       </c>
       <c r="I23" t="n">
-        <v>-11.4861</v>
+        <v>3.9648</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.288200000000001</v>
+        <v>19.8597</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.69</v>
+        <v>7.8177</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.598</v>
+        <v>12.0416</v>
       </c>
       <c r="M23" t="n">
-        <v>-11.1452</v>
+        <v>-22.9174</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.2572</v>
+        <v>-14.8406</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.8882</v>
+        <v>-8.076499999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>5.7439</v>
+        <v>5.559</v>
       </c>
       <c r="Q23" t="n">
-        <v>-20.3816</v>
+        <v>-23.5314</v>
       </c>
       <c r="R23" t="n">
-        <v>26.1253</v>
+        <v>29.09</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.965</v>
+        <v>-2.3944</v>
       </c>
       <c r="T23" t="n">
-        <v>-6.3841</v>
+        <v>-3.1251</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5811</v>
+        <v>0.7306999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-9.378299999999999</v>
+        <v>-25.8638</v>
       </c>
       <c r="W23" t="n">
-        <v>2.8311</v>
+        <v>1.2571</v>
       </c>
       <c r="X23" t="n">
-        <v>-12.2093</v>
+        <v>-27.1209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>A. GALLEGO GOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2278,76 +2278,76 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>-33.1064</v>
+        <v>-26.4773</v>
       </c>
       <c r="E24" t="n">
-        <v>-27.1604</v>
+        <v>-29.2729</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.946000000000002</v>
+        <v>2.7959</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.1393</v>
+        <v>-18.4335</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.0067</v>
+        <v>-6.9472</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.133</v>
+        <v>-11.4861</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7312</v>
+        <v>-7.288200000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4566</v>
+        <v>-1.69</v>
       </c>
       <c r="L24" t="n">
-        <v>2.2746</v>
+        <v>-5.598</v>
       </c>
       <c r="M24" t="n">
-        <v>-11.8705</v>
+        <v>-11.1452</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.4628</v>
+        <v>-5.2572</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.4074</v>
+        <v>-5.8882</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.040800000000001</v>
+        <v>5.7439</v>
       </c>
       <c r="Q24" t="n">
-        <v>-38.5395</v>
+        <v>-20.3816</v>
       </c>
       <c r="R24" t="n">
-        <v>31.499</v>
+        <v>26.1253</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.9217</v>
+        <v>-4.4098</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.9364</v>
+        <v>-4.434200000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.9858</v>
+        <v>0.02439999999999987</v>
       </c>
       <c r="V24" t="n">
-        <v>-10.0045</v>
+        <v>-9.378299999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>12.5846</v>
+        <v>2.8311</v>
       </c>
       <c r="X24" t="n">
-        <v>-22.5892</v>
+        <v>-12.2093</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,70 +2356,70 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>-37.1249</v>
+        <v>-26.8221</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.8441</v>
+        <v>-23.4248</v>
       </c>
       <c r="F25" t="n">
-        <v>-24.2805</v>
+        <v>-3.3974</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.058099999999999</v>
+        <v>-7.1393</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.0229</v>
+        <v>-6.0067</v>
       </c>
       <c r="I25" t="n">
-        <v>3.9648</v>
+        <v>-1.133</v>
       </c>
       <c r="J25" t="n">
-        <v>19.8597</v>
+        <v>4.7312</v>
       </c>
       <c r="K25" t="n">
-        <v>7.8177</v>
+        <v>2.4566</v>
       </c>
       <c r="L25" t="n">
-        <v>12.0416</v>
+        <v>2.2746</v>
       </c>
       <c r="M25" t="n">
-        <v>-22.9174</v>
+        <v>-11.8705</v>
       </c>
       <c r="N25" t="n">
-        <v>-14.8406</v>
+        <v>-8.4628</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.076499999999999</v>
+        <v>-3.4074</v>
       </c>
       <c r="P25" t="n">
-        <v>5.559</v>
+        <v>-7.040800000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-23.5314</v>
+        <v>-38.5395</v>
       </c>
       <c r="R25" t="n">
-        <v>29.09</v>
+        <v>31.499</v>
       </c>
       <c r="S25" t="n">
-        <v>-13.7619</v>
+        <v>-2.6374</v>
       </c>
       <c r="T25" t="n">
-        <v>-10.4292</v>
+        <v>-2.2008</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.3326</v>
+        <v>-0.4369999999999998</v>
       </c>
       <c r="V25" t="n">
-        <v>-25.8638</v>
+        <v>-10.0045</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2571</v>
+        <v>12.5846</v>
       </c>
       <c r="X25" t="n">
-        <v>-27.1209</v>
+        <v>-22.5892</v>
       </c>
     </row>
     <row r="26">
@@ -2437,22 +2437,22 @@
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>4.054600000000022</v>
+        <v>23.23699999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>20.52270000000001</v>
+        <v>25.9941</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.46759999999999</v>
+        <v>-2.7578</v>
       </c>
       <c r="G26" t="n">
-        <v>-21.2384</v>
+        <v>-21.23839999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-29.2617</v>
+        <v>-29.26169999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>8.023399999999995</v>
+        <v>8.023400000000001</v>
       </c>
       <c r="J26" t="n">
         <v>232.337</v>
@@ -2473,7 +2473,7 @@
         <v>-73.5</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9264000000000028</v>
+        <v>-0.9264000000000046</v>
       </c>
       <c r="Q26" t="n">
         <v>-418.7477</v>
@@ -2482,13 +2482,13 @@
         <v>417.8217</v>
       </c>
       <c r="S26" t="n">
-        <v>2.618199999999996</v>
+        <v>21.7986</v>
       </c>
       <c r="T26" t="n">
-        <v>-9.5273</v>
+        <v>-4.056100000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>12.145</v>
+        <v>25.8543</v>
       </c>
       <c r="V26" t="n">
         <v>23.602</v>
